--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_group_model.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_group_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE0AF00-EDED-4019-9959-EFC02CFFB6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD2B7BE-37A9-41EC-851C-FD25A84D035E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="468" yWindow="1860" windowWidth="19812" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="26610" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
   <si>
     <t>record_type</t>
   </si>
@@ -187,30 +187,12 @@
     <t>weighted_start</t>
   </si>
   <si>
-    <t>Spontaneousabortion_narrow_W82001</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>40348529</t>
   </si>
   <si>
-    <t>imputed_from_Spontaneousabortion_narrow</t>
-  </si>
-  <si>
-    <t>from_Spontaneousabortion_narrow</t>
-  </si>
-  <si>
     <t>SA</t>
   </si>
   <si>
-    <t>W82001</t>
-  </si>
-  <si>
-    <t>ICPC2P</t>
-  </si>
-  <si>
     <t>hospitalisation_primary</t>
   </si>
   <si>
@@ -239,6 +221,9 @@
   </si>
   <si>
     <t>40348529_record_1</t>
+  </si>
+  <si>
+    <t>person_1</t>
   </si>
 </sst>
 </file>
@@ -259,12 +244,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -279,9 +270,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -579,9 +582,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BC3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="27.140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="26.5703125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="22.42578125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="28" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="32" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="12" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="73.7109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="103.7109375" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="18.28515625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="9.5703125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="76" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="24.7109375" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="8" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="21.5703125" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="27.28515625" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="18" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="20.5703125" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="8.85546875" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="24.42578125" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="6" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="4" hidden="1" customWidth="1"/>
+    <col min="48" max="48" width="2.140625" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="30.42578125" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="29.85546875" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="26.85546875" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="23.7109375" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -748,285 +808,132 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:55" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5">
+        <v>40302</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="K2" s="5">
+        <v>40364</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2">
-        <v>35</v>
-      </c>
-      <c r="E2">
+      <c r="Z2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="AE2" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN2" s="4">
         <v>40364</v>
       </c>
-      <c r="G2" s="1">
+      <c r="AO2" s="4">
+        <v>40372</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="2">
+        <v>300</v>
+      </c>
+      <c r="AV2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="4">
+        <v>40294</v>
+      </c>
+      <c r="AX2" s="4"/>
+      <c r="AY2" s="4"/>
+      <c r="BA2" s="4">
+        <v>40364</v>
+      </c>
+      <c r="BB2" s="2">
+        <v>14725</v>
+      </c>
+      <c r="BC2" s="4">
         <v>40302</v>
       </c>
-      <c r="H2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="K2" s="1">
-        <v>40364</v>
-      </c>
-      <c r="L2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T2" t="s">
-        <v>64</v>
-      </c>
-      <c r="U2" t="s">
-        <v>65</v>
-      </c>
-      <c r="V2" t="s">
-        <v>66</v>
-      </c>
-      <c r="W2" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2">
-        <v>4</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>3</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN2" s="1">
-        <v>40364</v>
-      </c>
-      <c r="AO2" s="1">
-        <v>40372</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>300</v>
-      </c>
-      <c r="AV2">
-        <v>1</v>
-      </c>
-      <c r="AW2" s="1">
-        <v>40294</v>
-      </c>
-      <c r="AX2" s="1"/>
-      <c r="AY2" s="1"/>
-      <c r="BA2" s="1">
-        <v>40364</v>
-      </c>
-      <c r="BB2">
-        <v>14725</v>
-      </c>
-      <c r="BC2" s="1">
-        <v>40302</v>
-      </c>
     </row>
-    <row r="3" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3">
-        <v>35</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
-        <v>45838</v>
-      </c>
-      <c r="G3" s="1">
-        <v>40302</v>
-      </c>
-      <c r="H3" t="s">
-        <v>58</v>
-      </c>
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="K3" s="1">
-        <v>40364</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3" t="s">
-        <v>63</v>
-      </c>
-      <c r="S3" t="s">
-        <v>64</v>
-      </c>
-      <c r="T3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" t="s">
-        <v>65</v>
-      </c>
-      <c r="V3" t="s">
-        <v>66</v>
-      </c>
-      <c r="W3" t="s">
-        <v>64</v>
-      </c>
-      <c r="X3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z3">
-        <v>4</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>3</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN3" s="1">
-        <v>40364</v>
-      </c>
-      <c r="AO3" s="1">
-        <v>40372</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>300</v>
-      </c>
-      <c r="AV3">
-        <v>1</v>
-      </c>
-      <c r="AW3" s="1">
-        <v>40294</v>
-      </c>
+      <c r="K3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AW3" s="1"/>
       <c r="AX3" s="1"/>
       <c r="AY3" s="1"/>
-      <c r="BA3" s="1">
-        <v>40364</v>
-      </c>
-      <c r="BB3">
-        <v>14725</v>
-      </c>
-      <c r="BC3" s="1">
-        <v>40302</v>
-      </c>
+      <c r="BA3" s="1"/>
+      <c r="BC3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
